--- a/data/trans_dic/IMC_inf_MED_R2-Dificultad-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Dificultad-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5485985152616594</v>
+        <v>0.5394513918839032</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.4808004291001908</v>
+        <v>0.466919426301532</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.5459295882772127</v>
+        <v>0.5358208912282538</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.4866308558102792</v>
+        <v>0.485901205573558</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.3635498056915927</v>
+        <v>0.3522354480577291</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.2580489833353501</v>
+        <v>0.2943608081301614</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.5183088455425006</v>
+        <v>0.513481465838745</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.4253714772376245</v>
+        <v>0.413210461130649</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.4243666252087583</v>
+        <v>0.432861654465589</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.4878809449007006</v>
+        <v>0.4823418331700404</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.4262939637856952</v>
+        <v>0.4121502406809524</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.3985830930053235</v>
+        <v>0.392131233274489</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.4234741167300994</v>
+        <v>0.4231579704037719</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.310721296280061</v>
+        <v>0.3086784015498192</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.1380169353152618</v>
+        <v>0.1674111231796891</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.4733738435805489</v>
+        <v>0.4748941355304176</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.3881193159495689</v>
+        <v>0.3730669840683027</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.3194993429234006</v>
+        <v>0.3276742373652464</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.6077014241975511</v>
+        <v>0.5931628788391202</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.5424441188675454</v>
+        <v>0.5190130768475942</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.6801482728894859</v>
+        <v>0.6618453899673387</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5488027659627774</v>
+        <v>0.5424878798962334</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.426473636179685</v>
+        <v>0.4120938407942307</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.3898184038688926</v>
+        <v>0.4278837087047926</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5608044828143383</v>
+        <v>0.5568549420483124</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.4690090968295675</v>
+        <v>0.4516992853522911</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.5282754667571453</v>
+        <v>0.5343695621706472</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5799651498898299</v>
+        <v>0.5495807751474314</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.4210536408878094</v>
+        <v>0.4361931027382643</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.3821486638094868</v>
+        <v>0.3788835616678229</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.443025755971494</v>
+        <v>0.4318603798107185</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.348925956755124</v>
+        <v>0.3466771652487887</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.3110845210750064</v>
+        <v>0.3021247620682313</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.5133140141494416</v>
+        <v>0.4912099463844857</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.3855160608353929</v>
+        <v>0.3919970250334819</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.3523333570703633</v>
+        <v>0.3462138190625281</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.5191572800104644</v>
+        <v>0.4892962631790516</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.3566772236050965</v>
+        <v>0.3732581228575776</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2931408455828541</v>
+        <v>0.288607209675715</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3745672028353506</v>
+        <v>0.3686142223512505</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.2913230338726246</v>
+        <v>0.2887512155740596</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.221077222718526</v>
+        <v>0.2187833201185154</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4662862416687281</v>
+        <v>0.4481587129007674</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.3418229491682889</v>
+        <v>0.3515762777590758</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.2813042987058347</v>
+        <v>0.2837180313893994</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.6446298346245768</v>
+        <v>0.6075870884891789</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.4839171267309413</v>
+        <v>0.4961057049156432</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5015572031463227</v>
+        <v>0.484880495143524</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.5114479501347368</v>
+        <v>0.4870830280401883</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.4178677879491109</v>
+        <v>0.4125559178717221</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.4138685229087397</v>
+        <v>0.4031316324402022</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5586098525300687</v>
+        <v>0.5349234590043802</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.4370345511664972</v>
+        <v>0.4382365184806213</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.4303842724623547</v>
+        <v>0.4217829464640741</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.4860180086282767</v>
+        <v>0.4615316026568044</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.4418843677908274</v>
+        <v>0.4436083712883959</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.4364608613826682</v>
+        <v>0.4434953044649755</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3819214476362632</v>
+        <v>0.3898486877322933</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.3491576224419711</v>
+        <v>0.3385671070738551</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.2780196482932689</v>
+        <v>0.2892629616967015</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.4337710316329528</v>
+        <v>0.4260783476213989</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.3957809208434637</v>
+        <v>0.3912626172542592</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.3674097723725495</v>
+        <v>0.3767763985375625</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4084830562336539</v>
+        <v>0.3891350748329719</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.3603708523609565</v>
+        <v>0.370821937454814</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3389979093405031</v>
+        <v>0.3603735446152762</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.3097319748095254</v>
+        <v>0.3184869569120726</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2779620716403925</v>
+        <v>0.2749777731278998</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.1959563128245243</v>
+        <v>0.2108382093821911</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.3808444959501786</v>
+        <v>0.3767375774828189</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.3433753506646349</v>
+        <v>0.34166752270369</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.3105680788426949</v>
+        <v>0.3128619022225714</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5651068144927311</v>
+        <v>0.5282092706288272</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.5256966820339218</v>
+        <v>0.5197221614528056</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.5255257951168506</v>
+        <v>0.5263845328246231</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.4675083254724131</v>
+        <v>0.4554237368143803</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.432118672309483</v>
+        <v>0.4095257275082025</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.3596326594295881</v>
+        <v>0.3749196217870289</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.4925100430534096</v>
+        <v>0.4760178927471927</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.4524420329325499</v>
+        <v>0.443120028879644</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.4297817810211579</v>
+        <v>0.4425724458956188</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.4559556889530917</v>
+        <v>0.4777044104511418</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.4588541715231488</v>
+        <v>0.4313257746723418</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.2986164430726855</v>
+        <v>0.2954312342944225</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.483706411545652</v>
+        <v>0.4942971057060551</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.3044543246009532</v>
+        <v>0.3111359678882574</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.2574717904838912</v>
+        <v>0.2648637045955468</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.4692388389836714</v>
+        <v>0.485448533465914</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.3895543770902994</v>
+        <v>0.3801221558702025</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.279313538987389</v>
+        <v>0.281093651543366</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.353270704816191</v>
+        <v>0.3844241291560295</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.3619560649182043</v>
+        <v>0.340420207789841</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.2024876261349445</v>
+        <v>0.2091379466278857</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3724284537940025</v>
+        <v>0.3954503529967355</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.2031880424417564</v>
+        <v>0.2210397256901133</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.1660917665239523</v>
+        <v>0.1846608010706891</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.3905496375167692</v>
+        <v>0.4100675924257361</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.3198243149175339</v>
+        <v>0.3151756850611297</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.2133491450985646</v>
+        <v>0.2176564264330454</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.5550980701712727</v>
+        <v>0.5842324752201639</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.559774681843234</v>
+        <v>0.5257369553825281</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4100011220195751</v>
+        <v>0.4075876680634968</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.5839763165506984</v>
+        <v>0.5959021790713257</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.4195980529919181</v>
+        <v>0.4194613714879256</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.3487673199304672</v>
+        <v>0.3716455733394739</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5410458226903844</v>
+        <v>0.551327244785368</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.4739499992583395</v>
+        <v>0.4477067314584152</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.3536163630876992</v>
+        <v>0.355536243555845</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.5336234893388987</v>
+        <v>0.5173232725418957</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.4528408337491344</v>
+        <v>0.449133584507334</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.4083289102848109</v>
+        <v>0.4082653181670117</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.4493702869290529</v>
+        <v>0.4481799647969205</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.3496595783211826</v>
+        <v>0.3431505511685058</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.2803903762062169</v>
+        <v>0.2884474664607529</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.4923648546905175</v>
+        <v>0.4835647167147402</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.4031963428714455</v>
+        <v>0.3986185762010701</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.3525656960884628</v>
+        <v>0.3559004558150249</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.495190029589317</v>
+        <v>0.4821123133352459</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.4184086793413084</v>
+        <v>0.4146723033744146</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3550210878770767</v>
+        <v>0.3571205124323846</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.413947317264619</v>
+        <v>0.4121578325308833</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.315872675388333</v>
+        <v>0.3099932966444192</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.2275668005661554</v>
+        <v>0.2414566191146476</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.4659105339311578</v>
+        <v>0.4612310662471268</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.3763562250721808</v>
+        <v>0.3767637976743126</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3168929205289492</v>
+        <v>0.3187574239914105</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5695726695894925</v>
+        <v>0.5493711048680652</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.4906835230739187</v>
+        <v>0.4815810802932842</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.4669820706482208</v>
+        <v>0.4579566635104974</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.4871982796117309</v>
+        <v>0.4809760134795105</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.3860583987359593</v>
+        <v>0.376495428212155</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.330782587027325</v>
+        <v>0.3378011960510188</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.5167530499710475</v>
+        <v>0.5065547285028233</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.4288093517483217</v>
+        <v>0.4241210042793997</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.3915598109354776</v>
+        <v>0.3915855991106291</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1313,31 +1313,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1348,31 +1348,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>95358</v>
+        <v>114849</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>95495</v>
+        <v>115019</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>23189</v>
+        <v>24241</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>80880</v>
+        <v>97409</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>64741</v>
+        <v>76428</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>8012</v>
+        <v>9900</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>176238</v>
+        <v>212258</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>160236</v>
+        <v>191447</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>31201</v>
+        <v>34141</v>
       </c>
     </row>
     <row r="6">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>84804</v>
+        <v>102691</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>84669</v>
+        <v>101527</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>16931</v>
+        <v>17740</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>70383</v>
+        <v>84830</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>55333</v>
+        <v>66977</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>4285</v>
+        <v>5630</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>160959</v>
+        <v>196307</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>146203</v>
+        <v>172848</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>23491</v>
+        <v>25844</v>
       </c>
     </row>
     <row r="7">
@@ -1418,31 +1418,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>105632</v>
+        <v>126284</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>107739</v>
+        <v>127852</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>28891</v>
+        <v>29943</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>91213</v>
+        <v>108753</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>75946</v>
+        <v>89417</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>12103</v>
+        <v>14390</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>190688</v>
+        <v>230187</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>176674</v>
+        <v>209280</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>38841</v>
+        <v>42147</v>
       </c>
     </row>
     <row r="8">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>94035</v>
+        <v>100279</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>62930</v>
+        <v>74127</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>35059</v>
+        <v>36305</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>68115</v>
+        <v>77500</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>50650</v>
+        <v>57453</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>20629</v>
+        <v>21452</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>162150</v>
+        <v>177778</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>113580</v>
+        <v>131580</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>55688</v>
+        <v>57756</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>84176</v>
+        <v>89279</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>53309</v>
+        <v>63431</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>26893</v>
+        <v>27655</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>57589</v>
+        <v>66150</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>42288</v>
+        <v>47854</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>14660</v>
+        <v>15534</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>147295</v>
+        <v>162197</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>100707</v>
+        <v>118012</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>44462</v>
+        <v>47331</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>104520</v>
+        <v>110863</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>72326</v>
+        <v>84308</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>46014</v>
+        <v>46462</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>78635</v>
+        <v>87409</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>60657</v>
+        <v>68371</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>27445</v>
+        <v>28624</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>176459</v>
+        <v>193598</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>128758</v>
+        <v>147101</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>68024</v>
+        <v>70363</v>
       </c>
     </row>
     <row r="12">
@@ -1601,31 +1601,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>51914</v>
+        <v>62508</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>47603</v>
+        <v>56029</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>43873</v>
+        <v>47062</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>41108</v>
+        <v>51669</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>37194</v>
+        <v>42478</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>21588</v>
+        <v>23402</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>93022</v>
+        <v>114177</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>84798</v>
+        <v>98507</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>65461</v>
+        <v>70465</v>
       </c>
     </row>
     <row r="14">
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>43632</v>
+        <v>52703</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>38822</v>
+        <v>46836</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>34076</v>
+        <v>38242</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>33338</v>
+        <v>42211</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>29610</v>
+        <v>34500</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>15216</v>
+        <v>17057</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>81672</v>
+        <v>100955</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>73570</v>
+        <v>86021</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>55333</v>
+        <v>58511</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>60362</v>
+        <v>71539</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>56632</v>
+        <v>65642</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>52826</v>
+        <v>55858</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>50320</v>
+        <v>60360</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>46032</v>
+        <v>51381</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>27925</v>
+        <v>30332</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>105618</v>
+        <v>127559</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>96938</v>
+        <v>111563</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>76573</v>
+        <v>82770</v>
       </c>
     </row>
     <row r="16">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>39</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>23</v>
-      </c>
       <c r="H16" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -1780,31 +1780,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>29540</v>
+        <v>36662</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>28839</v>
+        <v>35952</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>17068</v>
+        <v>17526</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>28772</v>
+        <v>33201</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>15582</v>
+        <v>19249</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>13006</v>
+        <v>13881</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>58312</v>
+        <v>69863</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>44420</v>
+        <v>55201</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>30074</v>
+        <v>31407</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>22887</v>
+        <v>29503</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>22749</v>
+        <v>28375</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>11574</v>
+        <v>12407</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>22153</v>
+        <v>26562</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>10399</v>
+        <v>13675</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>8390</v>
+        <v>9678</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>48533</v>
+        <v>59015</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>36469</v>
+        <v>45770</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>22972</v>
+        <v>24319</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>35963</v>
+        <v>44838</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>35181</v>
+        <v>43822</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>23434</v>
+        <v>24180</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>34736</v>
+        <v>40026</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>21475</v>
+        <v>25951</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>17617</v>
+        <v>19477</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>67235</v>
+        <v>79344</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>54044</v>
+        <v>65016</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>38074</v>
+        <v>39725</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>388</v>
+        <v>446</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>333</v>
+        <v>399</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>700</v>
+        <v>816</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>583</v>
+        <v>692</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>270847</v>
+        <v>314299</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>234867</v>
+        <v>281127</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>119190</v>
+        <v>125135</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>218874</v>
+        <v>259777</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>168167</v>
+        <v>195609</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>63234</v>
+        <v>68634</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>489721</v>
+        <v>574076</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>403034</v>
+        <v>476736</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>182423</v>
+        <v>193769</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>251340</v>
+        <v>292906</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>217008</v>
+        <v>259556</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>103629</v>
+        <v>109459</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>201621</v>
+        <v>238898</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>151917</v>
+        <v>176708</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>51321</v>
+        <v>57453</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>463409</v>
+        <v>547562</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>376205</v>
+        <v>450598</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>163966</v>
+        <v>173547</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>289093</v>
+        <v>333769</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>254494</v>
+        <v>301437</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>136310</v>
+        <v>140366</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>237299</v>
+        <v>278787</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>185673</v>
+        <v>214617</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>74598</v>
+        <v>80378</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>513979</v>
+        <v>601369</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>428637</v>
+        <v>507236</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>202600</v>
+        <v>213198</v>
       </c>
     </row>
     <row r="24">
